--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B73249-29E9-433B-8E4F-60FF25CA64EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9DE9D5-FE69-42EA-AAC9-D25A2C5E829F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -971,7 +971,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1106,8 +1106,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1287,6 +1295,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1404,7 +1418,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1447,11 +1461,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1485,6 +1503,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1829,22 +1848,23 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
-    <col min="2" max="2" width="31.90625" customWidth="1"/>
-    <col min="3" max="3" width="68.26953125" customWidth="1"/>
+    <col min="2" max="2" width="61" customWidth="1"/>
+    <col min="3" max="3" width="142.08984375" customWidth="1"/>
+    <col min="4" max="4" width="4.81640625" customWidth="1"/>
     <col min="5" max="5" width="68.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1852,7 +1872,7 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
@@ -1866,7 +1886,7 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
@@ -1880,7 +1900,7 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
@@ -1894,10 +1914,10 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
@@ -1908,10 +1928,10 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
@@ -1922,10 +1942,10 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
@@ -1936,7 +1956,7 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
@@ -1950,10 +1970,10 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D9" t="s">
@@ -1964,10 +1984,10 @@
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
@@ -1992,10 +2012,10 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D12" t="s">
@@ -2006,10 +2026,10 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D13" t="s">
@@ -2020,7 +2040,7 @@
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C14" t="s">
@@ -2034,10 +2054,10 @@
       <c r="A15" t="s">
         <v>4</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D15" t="s">
@@ -2048,7 +2068,7 @@
       <c r="A16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C16" t="s">
@@ -2076,10 +2096,10 @@
       <c r="A18" t="s">
         <v>8</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D18" t="s">
@@ -2090,7 +2110,7 @@
       <c r="A19" t="s">
         <v>8</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C19" t="s">
@@ -2104,10 +2124,10 @@
       <c r="A20" t="s">
         <v>4</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D20" t="s">
@@ -2118,10 +2138,10 @@
       <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D21" t="s">
@@ -2132,10 +2152,10 @@
       <c r="A22" t="s">
         <v>8</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D22" t="s">
@@ -2146,10 +2166,10 @@
       <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D23" t="s">
@@ -2160,10 +2180,10 @@
       <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
@@ -2174,10 +2194,10 @@
       <c r="A25" t="s">
         <v>8</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D25" t="s">
@@ -2188,10 +2208,10 @@
       <c r="A26" t="s">
         <v>8</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D26" t="s">
@@ -2202,10 +2222,10 @@
       <c r="A27" t="s">
         <v>8</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D27" t="s">
@@ -2216,10 +2236,10 @@
       <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D28" t="s">
@@ -2230,10 +2250,10 @@
       <c r="A29" t="s">
         <v>8</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D29" t="s">
@@ -2244,10 +2264,10 @@
       <c r="A30" t="s">
         <v>4</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D30" t="s">
@@ -2258,10 +2278,10 @@
       <c r="A31" t="s">
         <v>8</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D31" t="s">
@@ -2272,10 +2292,10 @@
       <c r="A32" t="s">
         <v>12</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D32" t="s">
@@ -2286,10 +2306,10 @@
       <c r="A33" t="s">
         <v>12</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D33" t="s">
@@ -2300,10 +2320,10 @@
       <c r="A34" t="s">
         <v>12</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D34" t="s">
@@ -2314,7 +2334,7 @@
       <c r="A35" t="s">
         <v>4</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C35" t="s">
@@ -2328,10 +2348,10 @@
       <c r="A36" t="s">
         <v>8</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D36" t="s">
@@ -2342,10 +2362,10 @@
       <c r="A37" t="s">
         <v>4</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D37" t="s">
@@ -2356,10 +2376,10 @@
       <c r="A38" t="s">
         <v>12</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D38" t="s">
@@ -2370,10 +2390,10 @@
       <c r="A39" t="s">
         <v>8</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D39" t="s">
@@ -2384,7 +2404,7 @@
       <c r="A40" t="s">
         <v>8</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C40" t="s">
@@ -2398,10 +2418,10 @@
       <c r="A41" t="s">
         <v>8</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D41" t="s">
@@ -2412,10 +2432,10 @@
       <c r="A42" t="s">
         <v>4</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D42" t="s">
@@ -2426,10 +2446,10 @@
       <c r="A43" t="s">
         <v>8</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D43" t="s">
@@ -2440,10 +2460,10 @@
       <c r="A44" t="s">
         <v>12</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D44" t="s">
@@ -2454,10 +2474,10 @@
       <c r="A45" t="s">
         <v>4</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
@@ -2468,10 +2488,10 @@
       <c r="A46" t="s">
         <v>4</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="2" t="s">
         <v>136</v>
       </c>
       <c r="D46" t="s">
@@ -2482,7 +2502,7 @@
       <c r="A47" t="s">
         <v>12</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C47" t="s">
@@ -2496,10 +2516,10 @@
       <c r="A48" t="s">
         <v>4</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="2" t="s">
         <v>142</v>
       </c>
       <c r="D48" t="s">
@@ -2513,7 +2533,7 @@
       <c r="B49" t="s">
         <v>143</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D49" t="s">
@@ -2524,10 +2544,10 @@
       <c r="A50" t="s">
         <v>8</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D50" t="s">
@@ -2538,10 +2558,10 @@
       <c r="A51" t="s">
         <v>8</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D51" t="s">
@@ -2552,10 +2572,10 @@
       <c r="A52" t="s">
         <v>8</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="2" t="s">
         <v>153</v>
       </c>
       <c r="D52" t="s">
@@ -2566,7 +2586,7 @@
       <c r="A53" t="s">
         <v>4</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C53" t="s">
@@ -2580,10 +2600,10 @@
       <c r="A54" t="s">
         <v>4</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D54" t="s">
@@ -2594,10 +2614,10 @@
       <c r="A55" t="s">
         <v>4</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="2" t="s">
         <v>162</v>
       </c>
       <c r="D55" t="s">
@@ -2608,10 +2628,10 @@
       <c r="A56" t="s">
         <v>4</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="2" t="s">
         <v>165</v>
       </c>
       <c r="D56" t="s">
@@ -2622,10 +2642,10 @@
       <c r="A57" t="s">
         <v>8</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D57" t="s">
@@ -2636,10 +2656,10 @@
       <c r="A58" t="s">
         <v>4</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D58" t="s">
@@ -2650,10 +2670,10 @@
       <c r="A59" t="s">
         <v>8</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D59" t="s">
@@ -2664,7 +2684,7 @@
       <c r="A60" t="s">
         <v>8</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C60" t="s">
@@ -2678,10 +2698,10 @@
       <c r="A61" t="s">
         <v>4</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="2" t="s">
         <v>179</v>
       </c>
       <c r="D61" t="s">
@@ -2692,10 +2712,10 @@
       <c r="A62" t="s">
         <v>8</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="2" t="s">
         <v>181</v>
       </c>
       <c r="D62" t="s">
@@ -2706,10 +2726,10 @@
       <c r="A63" t="s">
         <v>8</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="2" t="s">
         <v>184</v>
       </c>
       <c r="D63" t="s">
@@ -2720,10 +2740,10 @@
       <c r="A64" t="s">
         <v>4</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="2" t="s">
         <v>186</v>
       </c>
       <c r="D64" t="s">
@@ -2734,10 +2754,10 @@
       <c r="A65" t="s">
         <v>8</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="2" t="s">
         <v>189</v>
       </c>
       <c r="D65" t="s">
@@ -2748,10 +2768,10 @@
       <c r="A66" t="s">
         <v>12</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="2" t="s">
         <v>192</v>
       </c>
       <c r="D66" t="s">
@@ -2762,10 +2782,10 @@
       <c r="A67" t="s">
         <v>8</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D67" t="s">
@@ -2776,10 +2796,10 @@
       <c r="A68" t="s">
         <v>8</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="2" t="s">
         <v>197</v>
       </c>
       <c r="D68" t="s">
@@ -2790,10 +2810,10 @@
       <c r="A69" t="s">
         <v>8</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="2" t="s">
         <v>200</v>
       </c>
       <c r="D69" t="s">
@@ -2804,10 +2824,10 @@
       <c r="A70" t="s">
         <v>8</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="2" t="s">
         <v>203</v>
       </c>
       <c r="D70" t="s">
@@ -2818,10 +2838,10 @@
       <c r="A71" t="s">
         <v>8</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="2" t="s">
         <v>205</v>
       </c>
       <c r="D71" t="s">
@@ -2832,10 +2852,10 @@
       <c r="A72" t="s">
         <v>8</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="2" t="s">
         <v>208</v>
       </c>
       <c r="D72" t="s">
@@ -2846,10 +2866,10 @@
       <c r="A73" t="s">
         <v>8</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="2" t="s">
         <v>210</v>
       </c>
       <c r="D73" t="s">
@@ -2860,10 +2880,10 @@
       <c r="A74" t="s">
         <v>4</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="2" t="s">
         <v>212</v>
       </c>
       <c r="D74" t="s">
@@ -2874,10 +2894,10 @@
       <c r="A75" t="s">
         <v>4</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D75" t="s">
@@ -2891,7 +2911,7 @@
       <c r="B76" t="s">
         <v>217</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="2" t="s">
         <v>218</v>
       </c>
       <c r="D76" t="s">
@@ -2902,10 +2922,10 @@
       <c r="A77" t="s">
         <v>8</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="2" t="s">
         <v>221</v>
       </c>
       <c r="D77" t="s">
@@ -2916,10 +2936,10 @@
       <c r="A78" t="s">
         <v>8</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="2" t="s">
         <v>224</v>
       </c>
       <c r="D78" t="s">
@@ -2930,10 +2950,10 @@
       <c r="A79" t="s">
         <v>8</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="2" t="s">
         <v>227</v>
       </c>
       <c r="D79" t="s">
@@ -2944,10 +2964,10 @@
       <c r="A80" t="s">
         <v>8</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="2" t="s">
         <v>229</v>
       </c>
       <c r="D80" t="s">
@@ -2958,10 +2978,10 @@
       <c r="A81" t="s">
         <v>8</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="2" t="s">
         <v>232</v>
       </c>
       <c r="D81" t="s">
@@ -2975,7 +2995,7 @@
       <c r="B82" t="s">
         <v>234</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="2" t="s">
         <v>235</v>
       </c>
       <c r="D82" t="s">
@@ -2986,10 +3006,10 @@
       <c r="A83" t="s">
         <v>12</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="2" t="s">
         <v>238</v>
       </c>
       <c r="D83" t="s">
@@ -3028,10 +3048,10 @@
       <c r="A86" t="s">
         <v>8</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="2" t="s">
         <v>246</v>
       </c>
       <c r="D86" t="s">
@@ -3045,7 +3065,7 @@
       <c r="B87" t="s">
         <v>248</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="2" t="s">
         <v>249</v>
       </c>
       <c r="D87" t="s">
@@ -3059,7 +3079,7 @@
       <c r="B88" t="s">
         <v>251</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="2" t="s">
         <v>252</v>
       </c>
       <c r="D88" t="s">
@@ -3073,7 +3093,7 @@
       <c r="B89" t="s">
         <v>254</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="2" t="s">
         <v>255</v>
       </c>
       <c r="D89" t="s">
@@ -3087,7 +3107,7 @@
       <c r="B90" t="s">
         <v>257</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="2" t="s">
         <v>258</v>
       </c>
       <c r="D90" t="s">
@@ -3101,7 +3121,7 @@
       <c r="B91" t="s">
         <v>259</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="2" t="s">
         <v>260</v>
       </c>
       <c r="D91" t="s">
@@ -3115,7 +3135,7 @@
       <c r="B92" t="s">
         <v>262</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="2" t="s">
         <v>263</v>
       </c>
       <c r="D92" t="s">
@@ -3129,7 +3149,7 @@
       <c r="B93" t="s">
         <v>265</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="2" t="s">
         <v>266</v>
       </c>
       <c r="D93" t="s">
@@ -3143,7 +3163,7 @@
       <c r="B94" t="s">
         <v>268</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="2" t="s">
         <v>269</v>
       </c>
       <c r="D94" t="s">
@@ -3157,7 +3177,7 @@
       <c r="B95" t="s">
         <v>271</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="2" t="s">
         <v>272</v>
       </c>
       <c r="D95" t="s">
@@ -3168,10 +3188,10 @@
       <c r="A96" t="s">
         <v>8</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="2" t="s">
         <v>275</v>
       </c>
       <c r="D96" t="s">
@@ -3185,7 +3205,7 @@
       <c r="B97" t="s">
         <v>277</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="2" t="s">
         <v>278</v>
       </c>
       <c r="D97" t="s">
@@ -3196,10 +3216,10 @@
       <c r="A98" t="s">
         <v>4</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="2" t="s">
         <v>280</v>
       </c>
       <c r="D98" t="s">
@@ -3213,7 +3233,7 @@
       <c r="B99" t="s">
         <v>281</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="2" t="s">
         <v>282</v>
       </c>
       <c r="D99" t="s">
@@ -3255,7 +3275,7 @@
       <c r="B102" t="s">
         <v>289</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="2" t="s">
         <v>290</v>
       </c>
       <c r="D102" t="s">
@@ -3283,7 +3303,7 @@
       <c r="B104" t="s">
         <v>295</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="2" t="s">
         <v>296</v>
       </c>
       <c r="D104" t="s">
@@ -3297,7 +3317,7 @@
       <c r="B105" t="s">
         <v>297</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="2" t="s">
         <v>298</v>
       </c>
       <c r="D105" t="s">
@@ -3322,10 +3342,10 @@
       <c r="A107" t="s">
         <v>8</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="2" t="s">
         <v>304</v>
       </c>
       <c r="D107" t="s">
@@ -3336,10 +3356,10 @@
       <c r="A108" t="s">
         <v>4</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="2" t="s">
         <v>306</v>
       </c>
       <c r="D108" t="s">
@@ -3353,7 +3373,7 @@
       <c r="B109" t="s">
         <v>307</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="2" t="s">
         <v>308</v>
       </c>
       <c r="D109" t="s">
@@ -3367,7 +3387,7 @@
       <c r="B110" t="s">
         <v>310</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="2" t="s">
         <v>311</v>
       </c>
       <c r="D110" t="s">
@@ -3378,14 +3398,107 @@
       <c r="A111" t="s">
         <v>12</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="2" t="s">
         <v>314</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{D6978A4C-3B34-4560-AE8B-3FB12802BA9F}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{2BB26076-BC0B-496D-9A8C-72B46335DA15}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{1FFF3911-BB8D-48A8-BD18-655BE1AD03E9}"/>
+    <hyperlink ref="C9" r:id="rId4" xr:uid="{DD9FEC9A-1DE1-41D2-B3EA-E3D1D2183761}"/>
+    <hyperlink ref="C10" r:id="rId5" xr:uid="{3010E1E8-2B79-49DF-8222-F860BCA75AFD}"/>
+    <hyperlink ref="C12" r:id="rId6" xr:uid="{E2A9E14A-F35D-4670-AD76-846BD8A4289B}"/>
+    <hyperlink ref="C13" r:id="rId7" xr:uid="{2FF95110-A6B2-4A47-AC6D-14C8F046B6C5}"/>
+    <hyperlink ref="C15" r:id="rId8" xr:uid="{65FB58F4-7FB8-4791-BB1A-E6E44DAD8E9A}"/>
+    <hyperlink ref="C18" r:id="rId9" xr:uid="{DFFE545C-4423-4888-9D1B-E4A5CF9DA710}"/>
+    <hyperlink ref="C20" r:id="rId10" xr:uid="{437C0ED0-0C98-4E50-AFF1-28CAD4AEC20E}"/>
+    <hyperlink ref="C21" r:id="rId11" xr:uid="{DCDF370A-6115-42AA-AA12-93DA12FA6D19}"/>
+    <hyperlink ref="C22" r:id="rId12" xr:uid="{9DD37778-C365-4B1E-8D70-B5F9B39AF0EB}"/>
+    <hyperlink ref="C23" r:id="rId13" xr:uid="{2E526343-8975-457E-8B17-F993792D7235}"/>
+    <hyperlink ref="C24" r:id="rId14" xr:uid="{B1FE6179-5A33-43AF-9C52-9E9563AC95D3}"/>
+    <hyperlink ref="C25" r:id="rId15" xr:uid="{EFB6E06F-2009-40FC-8619-BD3669A2E3E8}"/>
+    <hyperlink ref="C26" r:id="rId16" xr:uid="{A776D17F-94B7-4F20-9C74-F20100DE7CB3}"/>
+    <hyperlink ref="C27" r:id="rId17" xr:uid="{06D8518C-104E-4759-B687-794C7F2256E0}"/>
+    <hyperlink ref="C28" r:id="rId18" xr:uid="{C2FF1A15-816C-4176-B7D4-49824588E611}"/>
+    <hyperlink ref="C29" r:id="rId19" xr:uid="{15C61FD3-03FA-4179-8AE0-856E53A7052B}"/>
+    <hyperlink ref="C30" r:id="rId20" xr:uid="{8BEE6F0D-44B1-4F4A-8834-8AE37592C088}"/>
+    <hyperlink ref="C31" r:id="rId21" xr:uid="{D59F11BE-4517-4061-BC0B-550D78989CE1}"/>
+    <hyperlink ref="C32" r:id="rId22" xr:uid="{AF7D1AAF-5CA4-4154-9603-3E5C1FBF144A}"/>
+    <hyperlink ref="C33" r:id="rId23" xr:uid="{EF0A7D04-24D3-47BC-B4B0-C2AA6D70E558}"/>
+    <hyperlink ref="C34" r:id="rId24" xr:uid="{3414E615-B5A8-44F5-9413-E1D1019F9943}"/>
+    <hyperlink ref="C36" r:id="rId25" xr:uid="{5AE02E31-5A45-44C0-BD90-32F6EC874C7F}"/>
+    <hyperlink ref="C37" r:id="rId26" xr:uid="{AE62F543-8B97-446F-8477-FF680487331E}"/>
+    <hyperlink ref="C38" r:id="rId27" xr:uid="{42C6CB87-ABEF-4550-ADB4-7257F046709B}"/>
+    <hyperlink ref="C39" r:id="rId28" xr:uid="{86F5A7C6-8021-4BAC-9A70-D34F82DA6591}"/>
+    <hyperlink ref="C41" r:id="rId29" xr:uid="{D5A0FD1F-0302-4D2F-AB21-F4239C6B0C59}"/>
+    <hyperlink ref="C42" r:id="rId30" xr:uid="{BC787E3F-8A7F-4DA8-B178-80CB9FE5C252}"/>
+    <hyperlink ref="C43" r:id="rId31" xr:uid="{5B6CFA10-22F2-4D0A-9D79-F811C109B4D2}"/>
+    <hyperlink ref="C44" r:id="rId32" xr:uid="{2B63996F-AEFB-400E-BAE7-0DE6C5609E6E}"/>
+    <hyperlink ref="C45" r:id="rId33" xr:uid="{1AFD6EE5-183C-4D3C-880A-62B3A507956E}"/>
+    <hyperlink ref="C46" r:id="rId34" xr:uid="{AA14FD52-18C3-4562-913C-ED4687023239}"/>
+    <hyperlink ref="C48" r:id="rId35" xr:uid="{F6CB4C6C-4923-4B2B-A266-3B9288E3C496}"/>
+    <hyperlink ref="C49" r:id="rId36" xr:uid="{439DEC75-CE20-4B4E-91E7-F56030B0B617}"/>
+    <hyperlink ref="C50" r:id="rId37" xr:uid="{810DDA75-DA5C-47B0-9E72-E1CFD2FD98F0}"/>
+    <hyperlink ref="C51" r:id="rId38" xr:uid="{378D187A-E013-4121-BB87-E1796C8C5DA5}"/>
+    <hyperlink ref="C52" r:id="rId39" xr:uid="{F06D3027-FB45-4644-9E84-5368B9196EE6}"/>
+    <hyperlink ref="C54" r:id="rId40" xr:uid="{124C1375-FA58-4FF0-ACCC-A70B92F23214}"/>
+    <hyperlink ref="C55" r:id="rId41" xr:uid="{E2651A9E-E158-49AF-8120-3DCC5E6DFDB7}"/>
+    <hyperlink ref="C56" r:id="rId42" xr:uid="{8667A864-6594-4AF9-9E2B-F55451A1C2D2}"/>
+    <hyperlink ref="C57" r:id="rId43" xr:uid="{532E974C-8539-4B48-9933-79011AA045B6}"/>
+    <hyperlink ref="C58" r:id="rId44" xr:uid="{3532CEE5-A946-445F-882E-597323B01236}"/>
+    <hyperlink ref="C59" r:id="rId45" xr:uid="{6BCD875E-2238-4B4B-AAD8-DDA2B3DD7A97}"/>
+    <hyperlink ref="C61" r:id="rId46" xr:uid="{284EB028-7EBF-4985-93AD-3197012576B3}"/>
+    <hyperlink ref="C62" r:id="rId47" xr:uid="{1E80FEC3-559A-42BB-836C-9AAD0E406FA4}"/>
+    <hyperlink ref="C63" r:id="rId48" xr:uid="{3D8A005A-F633-4D58-99ED-415295CF807E}"/>
+    <hyperlink ref="C64" r:id="rId49" xr:uid="{EBC7DE65-FEBC-4959-B47D-3EC9C3B20504}"/>
+    <hyperlink ref="C65" r:id="rId50" xr:uid="{5A5D56CA-C6F3-458E-A572-DEF964B7FD17}"/>
+    <hyperlink ref="C66" r:id="rId51" xr:uid="{41DAF0FE-1A2B-4D21-82DC-81988E993BA4}"/>
+    <hyperlink ref="C68" r:id="rId52" xr:uid="{FE4CCFFB-9AC2-4F7F-98BC-DD2CA8969962}"/>
+    <hyperlink ref="C67" r:id="rId53" xr:uid="{B973CD6E-49EA-40AE-B9D4-82DDA5A1393B}"/>
+    <hyperlink ref="C69" r:id="rId54" xr:uid="{9F6D6C69-0C5B-4EA9-A223-CF5571B30716}"/>
+    <hyperlink ref="C70" r:id="rId55" xr:uid="{7F50146E-E96C-431A-B8F6-BD96AB9CCDA4}"/>
+    <hyperlink ref="C71" r:id="rId56" xr:uid="{5090B836-0CD0-4600-A975-512ADFB4C12C}"/>
+    <hyperlink ref="C72" r:id="rId57" xr:uid="{4A17FF77-A312-46BD-8DAE-4CA6EBE7483A}"/>
+    <hyperlink ref="C73" r:id="rId58" xr:uid="{B9B092B9-7B95-4B97-8D41-FB4D30E3E58C}"/>
+    <hyperlink ref="C74" r:id="rId59" xr:uid="{87C228E4-B5DF-4F42-809A-35D9D7F31239}"/>
+    <hyperlink ref="C75" r:id="rId60" xr:uid="{ABFA2CC5-517A-4F37-8B78-E38410B5F022}"/>
+    <hyperlink ref="C76" r:id="rId61" xr:uid="{663BDFC0-89D9-4092-9D05-4E0637991331}"/>
+    <hyperlink ref="C77" r:id="rId62" xr:uid="{A88845C8-A3E6-42C2-9F71-A33145A3C7F9}"/>
+    <hyperlink ref="C78" r:id="rId63" xr:uid="{ECB50AA5-3F65-4F2D-8F75-D6E9A6039BA1}"/>
+    <hyperlink ref="C79" r:id="rId64" xr:uid="{2B598789-ECBB-43B0-B592-91B673FF6759}"/>
+    <hyperlink ref="C80" r:id="rId65" xr:uid="{705F95FC-50D5-43B4-B6F4-9650EB377DEE}"/>
+    <hyperlink ref="C81" r:id="rId66" xr:uid="{A99BFAFD-FF2B-4B98-B770-0EBEA773B457}"/>
+    <hyperlink ref="C82" r:id="rId67" xr:uid="{1794B47E-843A-4BC3-879A-100CB9A53C14}"/>
+    <hyperlink ref="C83" r:id="rId68" xr:uid="{0493D93C-90A0-4678-B496-688F684326D5}"/>
+    <hyperlink ref="C86" r:id="rId69" xr:uid="{58BB325C-6A5F-433B-816E-F21A10A0A345}"/>
+    <hyperlink ref="C87" r:id="rId70" xr:uid="{2E57FD27-5B20-407F-B96E-839E08468505}"/>
+    <hyperlink ref="C89" r:id="rId71" xr:uid="{8DC4FD45-91C5-44FA-AB7A-51C978D7EAC0}"/>
+    <hyperlink ref="C88" r:id="rId72" xr:uid="{FE86A69A-745E-47EA-B3E5-748C15AA7981}"/>
+    <hyperlink ref="C90" r:id="rId73" xr:uid="{678D0ADF-289C-4C6A-B74F-AC326FEBE2C6}"/>
+    <hyperlink ref="C91" r:id="rId74" xr:uid="{E8B494CB-8606-4845-BD9F-72FF12D5B526}"/>
+    <hyperlink ref="C92" r:id="rId75" xr:uid="{7ACAAF9E-E73D-4511-BA0A-B0F95E48E038}"/>
+    <hyperlink ref="C93" r:id="rId76" xr:uid="{6CB594FF-B720-4F86-BC42-082B396A3F42}"/>
+    <hyperlink ref="C94" r:id="rId77" xr:uid="{0F7CE384-B7FE-4A1F-891D-30477D48ECA3}"/>
+    <hyperlink ref="C95" r:id="rId78" xr:uid="{ACB1200F-80D3-47CC-B90F-A1169A42FF15}"/>
+    <hyperlink ref="C96" r:id="rId79" xr:uid="{8B358065-E441-49F8-B2EF-085F688135A9}"/>
+    <hyperlink ref="C97" r:id="rId80" xr:uid="{E9B535D0-83B7-43C4-B77C-73F7EC8B9E72}"/>
+    <hyperlink ref="C98" r:id="rId81" xr:uid="{C1B2A205-43B4-4E5E-A4C4-E3EE79B6985B}"/>
+    <hyperlink ref="C99" r:id="rId82" xr:uid="{1AB0967C-D5DF-46DB-A9A3-4A5D08818AA1}"/>
+    <hyperlink ref="C102" r:id="rId83" xr:uid="{C5CF4C13-621E-4B4F-8AD3-777DC1777EC0}"/>
+    <hyperlink ref="C104" r:id="rId84" xr:uid="{0DCBE0F8-213E-4FFF-97C0-19E15C14BE50}"/>
+    <hyperlink ref="C105" r:id="rId85" xr:uid="{5C0CD156-5787-4B38-B502-83AF039E4663}"/>
+    <hyperlink ref="C107" r:id="rId86" xr:uid="{01026D67-5E4E-4093-98FE-8C2BB7F88CB9}"/>
+    <hyperlink ref="C108" r:id="rId87" xr:uid="{3EAC8E89-CB0A-4FA1-BAE1-A6CB74ECD8D9}"/>
+    <hyperlink ref="C109" r:id="rId88" xr:uid="{0C726199-E277-4D78-B4E4-2F9F38C7C18C}"/>
+    <hyperlink ref="C110" r:id="rId89" xr:uid="{8C941205-88A6-4243-925C-7716F11B3B3F}"/>
+    <hyperlink ref="C111" r:id="rId90" xr:uid="{83189FC4-0327-4B70-B9D7-DE95751C8E27}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId91"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9DE9D5-FE69-42EA-AAC9-D25A2C5E829F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713BA92A-C3C2-4059-B82E-3F2CBD2C2A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -2992,7 +2992,7 @@
       <c r="A82" t="s">
         <v>8</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C82" s="2" t="s">
@@ -3023,7 +3023,7 @@
       <c r="B84" t="s">
         <v>239</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D84" t="s">
@@ -3062,7 +3062,7 @@
       <c r="A87" t="s">
         <v>8</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>248</v>
       </c>
       <c r="C87" s="2" t="s">
@@ -3090,7 +3090,7 @@
       <c r="A89" t="s">
         <v>8</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>254</v>
       </c>
       <c r="C89" s="2" t="s">
@@ -3104,7 +3104,7 @@
       <c r="A90" t="s">
         <v>8</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>257</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -3497,8 +3497,9 @@
     <hyperlink ref="C109" r:id="rId88" xr:uid="{0C726199-E277-4D78-B4E4-2F9F38C7C18C}"/>
     <hyperlink ref="C110" r:id="rId89" xr:uid="{8C941205-88A6-4243-925C-7716F11B3B3F}"/>
     <hyperlink ref="C111" r:id="rId90" xr:uid="{83189FC4-0327-4B70-B9D7-DE95751C8E27}"/>
+    <hyperlink ref="C84" r:id="rId91" xr:uid="{F51CAEFD-286C-431E-8F9A-A4616D9F864D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId91"/>
+  <pageSetup orientation="portrait" r:id="rId92"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713BA92A-C3C2-4059-B82E-3F2CBD2C2A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B186401-E5F0-45C7-AEB3-815A0734A6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -1115,7 +1115,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1301,6 +1301,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1463,11 +1475,13 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1849,7 +1863,7 @@
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="61" customWidth="1"/>
-    <col min="3" max="3" width="142.08984375" customWidth="1"/>
+    <col min="3" max="3" width="59.90625" customWidth="1"/>
     <col min="4" max="4" width="4.81640625" customWidth="1"/>
     <col min="5" max="5" width="68.26953125" customWidth="1"/>
   </cols>
@@ -1998,14 +2012,14 @@
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -2013,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -2027,41 +2041,41 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -2069,41 +2083,41 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>52</v>
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -2111,27 +2125,27 @@
         <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>59</v>
+        <v>64</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -2139,13 +2153,13 @@
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -2153,13 +2167,13 @@
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -2167,13 +2181,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -2181,13 +2195,13 @@
         <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -2195,13 +2209,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -2209,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -2223,27 +2237,27 @@
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -2251,41 +2265,41 @@
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -2293,41 +2307,41 @@
         <v>12</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -2335,55 +2349,55 @@
         <v>4</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" t="s">
-        <v>105</v>
+        <v>109</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
+      </c>
+      <c r="C38" t="s">
+        <v>119</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -2391,27 +2405,27 @@
         <v>8</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" t="s">
-        <v>119</v>
+        <v>124</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -2419,69 +2433,69 @@
         <v>8</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2489,97 +2503,97 @@
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C47" t="s">
-        <v>139</v>
+        <v>146</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
-      <c r="B49" t="s">
-        <v>143</v>
+      <c r="B49" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
+      </c>
+      <c r="C50" t="s">
+        <v>156</v>
       </c>
       <c r="D50" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D51" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2587,27 +2601,27 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C53" t="s">
-        <v>156</v>
+        <v>164</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="D53" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D54" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -2615,27 +2629,27 @@
         <v>4</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D56" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -2643,13 +2657,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
+      </c>
+      <c r="C57" t="s">
+        <v>176</v>
       </c>
       <c r="D57" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -2657,13 +2671,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D58" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -2671,13 +2685,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -2685,13 +2699,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C60" t="s">
-        <v>176</v>
+        <v>183</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="D60" t="s">
-        <v>177</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -2699,13 +2713,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D61" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -2713,41 +2727,41 @@
         <v>8</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D62" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D64" t="s">
-        <v>187</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -2755,27 +2769,27 @@
         <v>8</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D65" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D66" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -2783,13 +2797,13 @@
         <v>8</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -2797,13 +2811,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D68" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -2811,13 +2825,13 @@
         <v>8</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D69" t="s">
-        <v>201</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
@@ -2825,41 +2839,41 @@
         <v>8</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D70" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D72" t="s">
-        <v>33</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
@@ -2867,55 +2881,55 @@
         <v>8</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D74" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D75" t="s">
-        <v>216</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
-      <c r="B76" t="s">
-        <v>217</v>
+      <c r="B76" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D76" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -2923,13 +2937,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D77" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
@@ -2937,27 +2951,27 @@
         <v>8</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D78" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D79" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
@@ -2965,13 +2979,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D80" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -2979,69 +2993,69 @@
         <v>8</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="D81" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>8</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>234</v>
+      <c r="B82" s="4" t="s">
+        <v>251</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="D82" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D83" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>8</v>
       </c>
-      <c r="B84" t="s">
-        <v>239</v>
+      <c r="B84" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="D84" t="s">
-        <v>241</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>8</v>
       </c>
-      <c r="B85" t="s">
-        <v>242</v>
-      </c>
-      <c r="C85" t="s">
-        <v>243</v>
+      <c r="B85" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="D85" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
@@ -3049,13 +3063,13 @@
         <v>8</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
@@ -3063,41 +3077,41 @@
         <v>8</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D87" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>8</v>
       </c>
-      <c r="B88" t="s">
-        <v>251</v>
+      <c r="B88" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="D88" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="D89" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
@@ -3105,265 +3119,262 @@
         <v>8</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="D90" t="s">
-        <v>83</v>
+        <v>283</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>8</v>
-      </c>
-      <c r="B91" t="s">
-        <v>259</v>
+        <v>4</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="D91" t="s">
-        <v>261</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>8</v>
       </c>
-      <c r="B92" t="s">
-        <v>262</v>
+      <c r="B92" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D92" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>8</v>
       </c>
-      <c r="B93" t="s">
-        <v>265</v>
+      <c r="B93" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="D93" t="s">
-        <v>267</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>8</v>
       </c>
-      <c r="B94" t="s">
-        <v>268</v>
+      <c r="B94" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D94" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>8</v>
       </c>
-      <c r="B95" t="s">
-        <v>271</v>
+      <c r="B95" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="D95" t="s">
-        <v>273</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="D96" t="s">
-        <v>276</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>8</v>
       </c>
-      <c r="B97" t="s">
-        <v>277</v>
+      <c r="B97" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D97" t="s">
-        <v>166</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D98" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>8</v>
       </c>
-      <c r="B99" t="s">
-        <v>281</v>
+      <c r="B99" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="D99" t="s">
-        <v>283</v>
+        <v>219</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>8</v>
       </c>
-      <c r="B100" t="s">
-        <v>284</v>
-      </c>
-      <c r="C100" t="s">
-        <v>285</v>
+      <c r="B100" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="D100" t="s">
-        <v>286</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>4</v>
-      </c>
-      <c r="B101" t="s">
-        <v>287</v>
-      </c>
-      <c r="C101" t="s">
-        <v>288</v>
+        <v>8</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="D101" t="s">
-        <v>39</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>8</v>
       </c>
-      <c r="B102" t="s">
-        <v>289</v>
+      <c r="B102" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="D102" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>8</v>
       </c>
-      <c r="B103" t="s">
-        <v>292</v>
-      </c>
-      <c r="C103" t="s">
-        <v>293</v>
+      <c r="B103" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="D103" t="s">
-        <v>294</v>
+        <v>166</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>8</v>
       </c>
-      <c r="B104" t="s">
-        <v>295</v>
+      <c r="B104" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D104" t="s">
-        <v>11</v>
+        <v>286</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>8</v>
       </c>
-      <c r="B105" t="s">
-        <v>297</v>
+      <c r="B105" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D105" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>8</v>
       </c>
-      <c r="B106" t="s">
-        <v>300</v>
-      </c>
-      <c r="C106" t="s">
-        <v>301</v>
+      <c r="B106" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="D106" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>8</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>304</v>
+      <c r="B107" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107" t="s">
+        <v>35</v>
       </c>
       <c r="D107" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>4</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>305</v>
+        <v>8</v>
+      </c>
+      <c r="B108" t="s">
+        <v>143</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>306</v>
+        <v>144</v>
       </c>
       <c r="D108" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
@@ -3371,13 +3382,13 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="D109" t="s">
-        <v>309</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
@@ -3385,24 +3396,27 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>310</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>311</v>
+        <v>52</v>
+      </c>
+      <c r="C110" t="s">
+        <v>53</v>
       </c>
       <c r="D110" t="s">
-        <v>312</v>
+        <v>54</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>12</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>313</v>
+      <c r="B111" t="s">
+        <v>310</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
+      </c>
+      <c r="D111" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -3412,94 +3426,99 @@
     <hyperlink ref="C7" r:id="rId3" xr:uid="{1FFF3911-BB8D-48A8-BD18-655BE1AD03E9}"/>
     <hyperlink ref="C9" r:id="rId4" xr:uid="{DD9FEC9A-1DE1-41D2-B3EA-E3D1D2183761}"/>
     <hyperlink ref="C10" r:id="rId5" xr:uid="{3010E1E8-2B79-49DF-8222-F860BCA75AFD}"/>
-    <hyperlink ref="C12" r:id="rId6" xr:uid="{E2A9E14A-F35D-4670-AD76-846BD8A4289B}"/>
-    <hyperlink ref="C13" r:id="rId7" xr:uid="{2FF95110-A6B2-4A47-AC6D-14C8F046B6C5}"/>
-    <hyperlink ref="C15" r:id="rId8" xr:uid="{65FB58F4-7FB8-4791-BB1A-E6E44DAD8E9A}"/>
-    <hyperlink ref="C18" r:id="rId9" xr:uid="{DFFE545C-4423-4888-9D1B-E4A5CF9DA710}"/>
-    <hyperlink ref="C20" r:id="rId10" xr:uid="{437C0ED0-0C98-4E50-AFF1-28CAD4AEC20E}"/>
-    <hyperlink ref="C21" r:id="rId11" xr:uid="{DCDF370A-6115-42AA-AA12-93DA12FA6D19}"/>
-    <hyperlink ref="C22" r:id="rId12" xr:uid="{9DD37778-C365-4B1E-8D70-B5F9B39AF0EB}"/>
-    <hyperlink ref="C23" r:id="rId13" xr:uid="{2E526343-8975-457E-8B17-F993792D7235}"/>
-    <hyperlink ref="C24" r:id="rId14" xr:uid="{B1FE6179-5A33-43AF-9C52-9E9563AC95D3}"/>
-    <hyperlink ref="C25" r:id="rId15" xr:uid="{EFB6E06F-2009-40FC-8619-BD3669A2E3E8}"/>
-    <hyperlink ref="C26" r:id="rId16" xr:uid="{A776D17F-94B7-4F20-9C74-F20100DE7CB3}"/>
-    <hyperlink ref="C27" r:id="rId17" xr:uid="{06D8518C-104E-4759-B687-794C7F2256E0}"/>
-    <hyperlink ref="C28" r:id="rId18" xr:uid="{C2FF1A15-816C-4176-B7D4-49824588E611}"/>
-    <hyperlink ref="C29" r:id="rId19" xr:uid="{15C61FD3-03FA-4179-8AE0-856E53A7052B}"/>
-    <hyperlink ref="C30" r:id="rId20" xr:uid="{8BEE6F0D-44B1-4F4A-8834-8AE37592C088}"/>
-    <hyperlink ref="C31" r:id="rId21" xr:uid="{D59F11BE-4517-4061-BC0B-550D78989CE1}"/>
-    <hyperlink ref="C32" r:id="rId22" xr:uid="{AF7D1AAF-5CA4-4154-9603-3E5C1FBF144A}"/>
-    <hyperlink ref="C33" r:id="rId23" xr:uid="{EF0A7D04-24D3-47BC-B4B0-C2AA6D70E558}"/>
-    <hyperlink ref="C34" r:id="rId24" xr:uid="{3414E615-B5A8-44F5-9413-E1D1019F9943}"/>
-    <hyperlink ref="C36" r:id="rId25" xr:uid="{5AE02E31-5A45-44C0-BD90-32F6EC874C7F}"/>
-    <hyperlink ref="C37" r:id="rId26" xr:uid="{AE62F543-8B97-446F-8477-FF680487331E}"/>
-    <hyperlink ref="C38" r:id="rId27" xr:uid="{42C6CB87-ABEF-4550-ADB4-7257F046709B}"/>
-    <hyperlink ref="C39" r:id="rId28" xr:uid="{86F5A7C6-8021-4BAC-9A70-D34F82DA6591}"/>
-    <hyperlink ref="C41" r:id="rId29" xr:uid="{D5A0FD1F-0302-4D2F-AB21-F4239C6B0C59}"/>
-    <hyperlink ref="C42" r:id="rId30" xr:uid="{BC787E3F-8A7F-4DA8-B178-80CB9FE5C252}"/>
-    <hyperlink ref="C43" r:id="rId31" xr:uid="{5B6CFA10-22F2-4D0A-9D79-F811C109B4D2}"/>
-    <hyperlink ref="C44" r:id="rId32" xr:uid="{2B63996F-AEFB-400E-BAE7-0DE6C5609E6E}"/>
-    <hyperlink ref="C45" r:id="rId33" xr:uid="{1AFD6EE5-183C-4D3C-880A-62B3A507956E}"/>
-    <hyperlink ref="C46" r:id="rId34" xr:uid="{AA14FD52-18C3-4562-913C-ED4687023239}"/>
-    <hyperlink ref="C48" r:id="rId35" xr:uid="{F6CB4C6C-4923-4B2B-A266-3B9288E3C496}"/>
-    <hyperlink ref="C49" r:id="rId36" xr:uid="{439DEC75-CE20-4B4E-91E7-F56030B0B617}"/>
-    <hyperlink ref="C50" r:id="rId37" xr:uid="{810DDA75-DA5C-47B0-9E72-E1CFD2FD98F0}"/>
-    <hyperlink ref="C51" r:id="rId38" xr:uid="{378D187A-E013-4121-BB87-E1796C8C5DA5}"/>
-    <hyperlink ref="C52" r:id="rId39" xr:uid="{F06D3027-FB45-4644-9E84-5368B9196EE6}"/>
-    <hyperlink ref="C54" r:id="rId40" xr:uid="{124C1375-FA58-4FF0-ACCC-A70B92F23214}"/>
-    <hyperlink ref="C55" r:id="rId41" xr:uid="{E2651A9E-E158-49AF-8120-3DCC5E6DFDB7}"/>
-    <hyperlink ref="C56" r:id="rId42" xr:uid="{8667A864-6594-4AF9-9E2B-F55451A1C2D2}"/>
-    <hyperlink ref="C57" r:id="rId43" xr:uid="{532E974C-8539-4B48-9933-79011AA045B6}"/>
-    <hyperlink ref="C58" r:id="rId44" xr:uid="{3532CEE5-A946-445F-882E-597323B01236}"/>
-    <hyperlink ref="C59" r:id="rId45" xr:uid="{6BCD875E-2238-4B4B-AAD8-DDA2B3DD7A97}"/>
-    <hyperlink ref="C61" r:id="rId46" xr:uid="{284EB028-7EBF-4985-93AD-3197012576B3}"/>
-    <hyperlink ref="C62" r:id="rId47" xr:uid="{1E80FEC3-559A-42BB-836C-9AAD0E406FA4}"/>
-    <hyperlink ref="C63" r:id="rId48" xr:uid="{3D8A005A-F633-4D58-99ED-415295CF807E}"/>
-    <hyperlink ref="C64" r:id="rId49" xr:uid="{EBC7DE65-FEBC-4959-B47D-3EC9C3B20504}"/>
-    <hyperlink ref="C65" r:id="rId50" xr:uid="{5A5D56CA-C6F3-458E-A572-DEF964B7FD17}"/>
-    <hyperlink ref="C66" r:id="rId51" xr:uid="{41DAF0FE-1A2B-4D21-82DC-81988E993BA4}"/>
-    <hyperlink ref="C68" r:id="rId52" xr:uid="{FE4CCFFB-9AC2-4F7F-98BC-DD2CA8969962}"/>
-    <hyperlink ref="C67" r:id="rId53" xr:uid="{B973CD6E-49EA-40AE-B9D4-82DDA5A1393B}"/>
-    <hyperlink ref="C69" r:id="rId54" xr:uid="{9F6D6C69-0C5B-4EA9-A223-CF5571B30716}"/>
-    <hyperlink ref="C70" r:id="rId55" xr:uid="{7F50146E-E96C-431A-B8F6-BD96AB9CCDA4}"/>
-    <hyperlink ref="C71" r:id="rId56" xr:uid="{5090B836-0CD0-4600-A975-512ADFB4C12C}"/>
-    <hyperlink ref="C72" r:id="rId57" xr:uid="{4A17FF77-A312-46BD-8DAE-4CA6EBE7483A}"/>
-    <hyperlink ref="C73" r:id="rId58" xr:uid="{B9B092B9-7B95-4B97-8D41-FB4D30E3E58C}"/>
-    <hyperlink ref="C74" r:id="rId59" xr:uid="{87C228E4-B5DF-4F42-809A-35D9D7F31239}"/>
-    <hyperlink ref="C75" r:id="rId60" xr:uid="{ABFA2CC5-517A-4F37-8B78-E38410B5F022}"/>
-    <hyperlink ref="C76" r:id="rId61" xr:uid="{663BDFC0-89D9-4092-9D05-4E0637991331}"/>
-    <hyperlink ref="C77" r:id="rId62" xr:uid="{A88845C8-A3E6-42C2-9F71-A33145A3C7F9}"/>
-    <hyperlink ref="C78" r:id="rId63" xr:uid="{ECB50AA5-3F65-4F2D-8F75-D6E9A6039BA1}"/>
-    <hyperlink ref="C79" r:id="rId64" xr:uid="{2B598789-ECBB-43B0-B592-91B673FF6759}"/>
-    <hyperlink ref="C80" r:id="rId65" xr:uid="{705F95FC-50D5-43B4-B6F4-9650EB377DEE}"/>
-    <hyperlink ref="C81" r:id="rId66" xr:uid="{A99BFAFD-FF2B-4B98-B770-0EBEA773B457}"/>
-    <hyperlink ref="C82" r:id="rId67" xr:uid="{1794B47E-843A-4BC3-879A-100CB9A53C14}"/>
-    <hyperlink ref="C83" r:id="rId68" xr:uid="{0493D93C-90A0-4678-B496-688F684326D5}"/>
-    <hyperlink ref="C86" r:id="rId69" xr:uid="{58BB325C-6A5F-433B-816E-F21A10A0A345}"/>
-    <hyperlink ref="C87" r:id="rId70" xr:uid="{2E57FD27-5B20-407F-B96E-839E08468505}"/>
-    <hyperlink ref="C89" r:id="rId71" xr:uid="{8DC4FD45-91C5-44FA-AB7A-51C978D7EAC0}"/>
-    <hyperlink ref="C88" r:id="rId72" xr:uid="{FE86A69A-745E-47EA-B3E5-748C15AA7981}"/>
-    <hyperlink ref="C90" r:id="rId73" xr:uid="{678D0ADF-289C-4C6A-B74F-AC326FEBE2C6}"/>
-    <hyperlink ref="C91" r:id="rId74" xr:uid="{E8B494CB-8606-4845-BD9F-72FF12D5B526}"/>
-    <hyperlink ref="C92" r:id="rId75" xr:uid="{7ACAAF9E-E73D-4511-BA0A-B0F95E48E038}"/>
-    <hyperlink ref="C93" r:id="rId76" xr:uid="{6CB594FF-B720-4F86-BC42-082B396A3F42}"/>
-    <hyperlink ref="C94" r:id="rId77" xr:uid="{0F7CE384-B7FE-4A1F-891D-30477D48ECA3}"/>
-    <hyperlink ref="C95" r:id="rId78" xr:uid="{ACB1200F-80D3-47CC-B90F-A1169A42FF15}"/>
-    <hyperlink ref="C96" r:id="rId79" xr:uid="{8B358065-E441-49F8-B2EF-085F688135A9}"/>
-    <hyperlink ref="C97" r:id="rId80" xr:uid="{E9B535D0-83B7-43C4-B77C-73F7EC8B9E72}"/>
-    <hyperlink ref="C98" r:id="rId81" xr:uid="{C1B2A205-43B4-4E5E-A4C4-E3EE79B6985B}"/>
-    <hyperlink ref="C99" r:id="rId82" xr:uid="{1AB0967C-D5DF-46DB-A9A3-4A5D08818AA1}"/>
-    <hyperlink ref="C102" r:id="rId83" xr:uid="{C5CF4C13-621E-4B4F-8AD3-777DC1777EC0}"/>
-    <hyperlink ref="C104" r:id="rId84" xr:uid="{0DCBE0F8-213E-4FFF-97C0-19E15C14BE50}"/>
-    <hyperlink ref="C105" r:id="rId85" xr:uid="{5C0CD156-5787-4B38-B502-83AF039E4663}"/>
-    <hyperlink ref="C107" r:id="rId86" xr:uid="{01026D67-5E4E-4093-98FE-8C2BB7F88CB9}"/>
-    <hyperlink ref="C108" r:id="rId87" xr:uid="{3EAC8E89-CB0A-4FA1-BAE1-A6CB74ECD8D9}"/>
-    <hyperlink ref="C109" r:id="rId88" xr:uid="{0C726199-E277-4D78-B4E4-2F9F38C7C18C}"/>
-    <hyperlink ref="C110" r:id="rId89" xr:uid="{8C941205-88A6-4243-925C-7716F11B3B3F}"/>
-    <hyperlink ref="C111" r:id="rId90" xr:uid="{83189FC4-0327-4B70-B9D7-DE95751C8E27}"/>
-    <hyperlink ref="C84" r:id="rId91" xr:uid="{F51CAEFD-286C-431E-8F9A-A4616D9F864D}"/>
+    <hyperlink ref="C11" r:id="rId6" xr:uid="{E2A9E14A-F35D-4670-AD76-846BD8A4289B}"/>
+    <hyperlink ref="C12" r:id="rId7" xr:uid="{2FF95110-A6B2-4A47-AC6D-14C8F046B6C5}"/>
+    <hyperlink ref="C14" r:id="rId8" xr:uid="{65FB58F4-7FB8-4791-BB1A-E6E44DAD8E9A}"/>
+    <hyperlink ref="C16" r:id="rId9" xr:uid="{DFFE545C-4423-4888-9D1B-E4A5CF9DA710}"/>
+    <hyperlink ref="C18" r:id="rId10" xr:uid="{437C0ED0-0C98-4E50-AFF1-28CAD4AEC20E}"/>
+    <hyperlink ref="C19" r:id="rId11" xr:uid="{DCDF370A-6115-42AA-AA12-93DA12FA6D19}"/>
+    <hyperlink ref="C20" r:id="rId12" xr:uid="{9DD37778-C365-4B1E-8D70-B5F9B39AF0EB}"/>
+    <hyperlink ref="C21" r:id="rId13" xr:uid="{2E526343-8975-457E-8B17-F993792D7235}"/>
+    <hyperlink ref="C22" r:id="rId14" xr:uid="{B1FE6179-5A33-43AF-9C52-9E9563AC95D3}"/>
+    <hyperlink ref="C23" r:id="rId15" xr:uid="{EFB6E06F-2009-40FC-8619-BD3669A2E3E8}"/>
+    <hyperlink ref="C24" r:id="rId16" xr:uid="{A776D17F-94B7-4F20-9C74-F20100DE7CB3}"/>
+    <hyperlink ref="C25" r:id="rId17" xr:uid="{06D8518C-104E-4759-B687-794C7F2256E0}"/>
+    <hyperlink ref="C26" r:id="rId18" xr:uid="{C2FF1A15-816C-4176-B7D4-49824588E611}"/>
+    <hyperlink ref="C27" r:id="rId19" xr:uid="{15C61FD3-03FA-4179-8AE0-856E53A7052B}"/>
+    <hyperlink ref="C28" r:id="rId20" xr:uid="{8BEE6F0D-44B1-4F4A-8834-8AE37592C088}"/>
+    <hyperlink ref="C29" r:id="rId21" xr:uid="{D59F11BE-4517-4061-BC0B-550D78989CE1}"/>
+    <hyperlink ref="C30" r:id="rId22" xr:uid="{AF7D1AAF-5CA4-4154-9603-3E5C1FBF144A}"/>
+    <hyperlink ref="C31" r:id="rId23" xr:uid="{EF0A7D04-24D3-47BC-B4B0-C2AA6D70E558}"/>
+    <hyperlink ref="C32" r:id="rId24" xr:uid="{3414E615-B5A8-44F5-9413-E1D1019F9943}"/>
+    <hyperlink ref="C34" r:id="rId25" xr:uid="{5AE02E31-5A45-44C0-BD90-32F6EC874C7F}"/>
+    <hyperlink ref="C35" r:id="rId26" xr:uid="{AE62F543-8B97-446F-8477-FF680487331E}"/>
+    <hyperlink ref="C36" r:id="rId27" xr:uid="{42C6CB87-ABEF-4550-ADB4-7257F046709B}"/>
+    <hyperlink ref="C37" r:id="rId28" xr:uid="{86F5A7C6-8021-4BAC-9A70-D34F82DA6591}"/>
+    <hyperlink ref="C39" r:id="rId29" xr:uid="{D5A0FD1F-0302-4D2F-AB21-F4239C6B0C59}"/>
+    <hyperlink ref="C40" r:id="rId30" xr:uid="{BC787E3F-8A7F-4DA8-B178-80CB9FE5C252}"/>
+    <hyperlink ref="C41" r:id="rId31" xr:uid="{5B6CFA10-22F2-4D0A-9D79-F811C109B4D2}"/>
+    <hyperlink ref="C42" r:id="rId32" xr:uid="{2B63996F-AEFB-400E-BAE7-0DE6C5609E6E}"/>
+    <hyperlink ref="C43" r:id="rId33" xr:uid="{1AFD6EE5-183C-4D3C-880A-62B3A507956E}"/>
+    <hyperlink ref="C44" r:id="rId34" xr:uid="{AA14FD52-18C3-4562-913C-ED4687023239}"/>
+    <hyperlink ref="C46" r:id="rId35" xr:uid="{F6CB4C6C-4923-4B2B-A266-3B9288E3C496}"/>
+    <hyperlink ref="C47" r:id="rId36" xr:uid="{810DDA75-DA5C-47B0-9E72-E1CFD2FD98F0}"/>
+    <hyperlink ref="C48" r:id="rId37" xr:uid="{378D187A-E013-4121-BB87-E1796C8C5DA5}"/>
+    <hyperlink ref="C49" r:id="rId38" xr:uid="{F06D3027-FB45-4644-9E84-5368B9196EE6}"/>
+    <hyperlink ref="C51" r:id="rId39" xr:uid="{124C1375-FA58-4FF0-ACCC-A70B92F23214}"/>
+    <hyperlink ref="C52" r:id="rId40" xr:uid="{E2651A9E-E158-49AF-8120-3DCC5E6DFDB7}"/>
+    <hyperlink ref="C53" r:id="rId41" xr:uid="{8667A864-6594-4AF9-9E2B-F55451A1C2D2}"/>
+    <hyperlink ref="C54" r:id="rId42" xr:uid="{532E974C-8539-4B48-9933-79011AA045B6}"/>
+    <hyperlink ref="C55" r:id="rId43" xr:uid="{3532CEE5-A946-445F-882E-597323B01236}"/>
+    <hyperlink ref="C56" r:id="rId44" xr:uid="{6BCD875E-2238-4B4B-AAD8-DDA2B3DD7A97}"/>
+    <hyperlink ref="C58" r:id="rId45" xr:uid="{284EB028-7EBF-4985-93AD-3197012576B3}"/>
+    <hyperlink ref="C59" r:id="rId46" xr:uid="{1E80FEC3-559A-42BB-836C-9AAD0E406FA4}"/>
+    <hyperlink ref="C60" r:id="rId47" xr:uid="{3D8A005A-F633-4D58-99ED-415295CF807E}"/>
+    <hyperlink ref="C61" r:id="rId48" xr:uid="{EBC7DE65-FEBC-4959-B47D-3EC9C3B20504}"/>
+    <hyperlink ref="C62" r:id="rId49" xr:uid="{5A5D56CA-C6F3-458E-A572-DEF964B7FD17}"/>
+    <hyperlink ref="C63" r:id="rId50" xr:uid="{41DAF0FE-1A2B-4D21-82DC-81988E993BA4}"/>
+    <hyperlink ref="C65" r:id="rId51" xr:uid="{FE4CCFFB-9AC2-4F7F-98BC-DD2CA8969962}"/>
+    <hyperlink ref="C64" r:id="rId52" xr:uid="{B973CD6E-49EA-40AE-B9D4-82DDA5A1393B}"/>
+    <hyperlink ref="C66" r:id="rId53" xr:uid="{9F6D6C69-0C5B-4EA9-A223-CF5571B30716}"/>
+    <hyperlink ref="C67" r:id="rId54" xr:uid="{7F50146E-E96C-431A-B8F6-BD96AB9CCDA4}"/>
+    <hyperlink ref="C68" r:id="rId55" xr:uid="{5090B836-0CD0-4600-A975-512ADFB4C12C}"/>
+    <hyperlink ref="C69" r:id="rId56" xr:uid="{4A17FF77-A312-46BD-8DAE-4CA6EBE7483A}"/>
+    <hyperlink ref="C70" r:id="rId57" xr:uid="{B9B092B9-7B95-4B97-8D41-FB4D30E3E58C}"/>
+    <hyperlink ref="C71" r:id="rId58" xr:uid="{87C228E4-B5DF-4F42-809A-35D9D7F31239}"/>
+    <hyperlink ref="C72" r:id="rId59" xr:uid="{ABFA2CC5-517A-4F37-8B78-E38410B5F022}"/>
+    <hyperlink ref="C73" r:id="rId60" xr:uid="{A88845C8-A3E6-42C2-9F71-A33145A3C7F9}"/>
+    <hyperlink ref="C74" r:id="rId61" xr:uid="{ECB50AA5-3F65-4F2D-8F75-D6E9A6039BA1}"/>
+    <hyperlink ref="C75" r:id="rId62" xr:uid="{2B598789-ECBB-43B0-B592-91B673FF6759}"/>
+    <hyperlink ref="C76" r:id="rId63" xr:uid="{705F95FC-50D5-43B4-B6F4-9650EB377DEE}"/>
+    <hyperlink ref="C77" r:id="rId64" xr:uid="{A99BFAFD-FF2B-4B98-B770-0EBEA773B457}"/>
+    <hyperlink ref="C78" r:id="rId65" xr:uid="{1794B47E-843A-4BC3-879A-100CB9A53C14}"/>
+    <hyperlink ref="C79" r:id="rId66" xr:uid="{0493D93C-90A0-4678-B496-688F684326D5}"/>
+    <hyperlink ref="C80" r:id="rId67" xr:uid="{58BB325C-6A5F-433B-816E-F21A10A0A345}"/>
+    <hyperlink ref="C81" r:id="rId68" xr:uid="{2E57FD27-5B20-407F-B96E-839E08468505}"/>
+    <hyperlink ref="C83" r:id="rId69" xr:uid="{8DC4FD45-91C5-44FA-AB7A-51C978D7EAC0}"/>
+    <hyperlink ref="C82" r:id="rId70" xr:uid="{FE86A69A-745E-47EA-B3E5-748C15AA7981}"/>
+    <hyperlink ref="C84" r:id="rId71" xr:uid="{678D0ADF-289C-4C6A-B74F-AC326FEBE2C6}"/>
+    <hyperlink ref="C85" r:id="rId72" xr:uid="{E8B494CB-8606-4845-BD9F-72FF12D5B526}"/>
+    <hyperlink ref="C86" r:id="rId73" xr:uid="{7ACAAF9E-E73D-4511-BA0A-B0F95E48E038}"/>
+    <hyperlink ref="C87" r:id="rId74" xr:uid="{6CB594FF-B720-4F86-BC42-082B396A3F42}"/>
+    <hyperlink ref="C88" r:id="rId75" xr:uid="{8B358065-E441-49F8-B2EF-085F688135A9}"/>
+    <hyperlink ref="C89" r:id="rId76" xr:uid="{C1B2A205-43B4-4E5E-A4C4-E3EE79B6985B}"/>
+    <hyperlink ref="C90" r:id="rId77" xr:uid="{1AB0967C-D5DF-46DB-A9A3-4A5D08818AA1}"/>
+    <hyperlink ref="C93" r:id="rId78" xr:uid="{0DCBE0F8-213E-4FFF-97C0-19E15C14BE50}"/>
+    <hyperlink ref="C95" r:id="rId79" xr:uid="{01026D67-5E4E-4093-98FE-8C2BB7F88CB9}"/>
+    <hyperlink ref="C96" r:id="rId80" xr:uid="{3EAC8E89-CB0A-4FA1-BAE1-A6CB74ECD8D9}"/>
+    <hyperlink ref="C97" r:id="rId81" xr:uid="{0C726199-E277-4D78-B4E4-2F9F38C7C18C}"/>
+    <hyperlink ref="C98" r:id="rId82" xr:uid="{83189FC4-0327-4B70-B9D7-DE95751C8E27}"/>
+    <hyperlink ref="C91" r:id="rId83" xr:uid="{740C1B3C-75FE-463F-8A02-21383B62FEFF}"/>
+    <hyperlink ref="C92" r:id="rId84" xr:uid="{393517DD-B13A-45EE-9B89-FB0F13633174}"/>
+    <hyperlink ref="C94" r:id="rId85" xr:uid="{B5FC891D-1D12-4A44-B2C4-7E649888E703}"/>
+    <hyperlink ref="C108" r:id="rId86" xr:uid="{16BACD8E-DE89-4579-A60A-4959D9A15B54}"/>
+    <hyperlink ref="C99" r:id="rId87" xr:uid="{1662E5AD-A595-41A8-9716-473ABF915976}"/>
+    <hyperlink ref="C100" r:id="rId88" xr:uid="{1B2EF9CE-43C1-42F2-B09F-31BDFF4ED857}"/>
+    <hyperlink ref="C101" r:id="rId89" xr:uid="{08A9E141-BAE2-4F77-8EE4-2107B86E726A}"/>
+    <hyperlink ref="C102" r:id="rId90" xr:uid="{AE5B0EE8-A04A-4CC3-A7D0-CE81C297EB2A}"/>
+    <hyperlink ref="C103" r:id="rId91" xr:uid="{5FC31869-36CF-4AA6-B713-6B1805D02AB2}"/>
+    <hyperlink ref="C104" r:id="rId92" xr:uid="{0D69B397-D861-4A5D-9397-1BE272E25022}"/>
+    <hyperlink ref="C105" r:id="rId93" xr:uid="{2C59DDBA-2D6F-4229-98AE-3A7C9586C72F}"/>
+    <hyperlink ref="C106" r:id="rId94" xr:uid="{E63386B9-D4BB-4EC2-ABBC-787D5C433C84}"/>
+    <hyperlink ref="C111" r:id="rId95" xr:uid="{7B68E9DB-3F88-42AA-A5B8-6C92BC7CCC4A}"/>
+    <hyperlink ref="C109" r:id="rId96" xr:uid="{FD6CDB59-0FF2-404F-A390-575C163418DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId92"/>
+  <pageSetup orientation="portrait" r:id="rId97"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B186401-E5F0-45C7-AEB3-815A0734A6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE5332E-0A96-4B75-A4A2-409342025B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="430">
   <si>
     <t>Difficulty</t>
   </si>
@@ -965,6 +965,351 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/merge-k-sorted-lists</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Maximum Coins From K Consecutive Bags</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minimum Operations to Make Array Non Decreasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Longest Common Prefix</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Maximum Product of Three Numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Palindrome Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add Binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the Index of the First Occurrence in a String</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Predict the Winner</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Roman to Integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reverse Integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Running Sum of 1d Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Concatenation of Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fibonacci Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stone Game II</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Valid Anagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Length of Longest Subarray With at Most K Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rotate Image</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> String to Integer (atoi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Count Primes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Smallest Subsequence of Distinct Characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Power of Two</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Happy Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multiply Strings</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Number of Unique XOR Triplets II</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Check if Array Is Sorted and Rotated</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reverse String</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Smallest Palindromic Rearrangement I</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Super Washing Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Largest Divisible Subset</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove Duplicate Letters</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kids With the Greatest Number of Candies</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ones and Zeroes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bulls and Cows</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minimum Number of Pushes to Type Word II</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Array Partition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Widest Possible Fence</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Set Mismatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shortest Subarray with Sum at Least K</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove Methods From Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ransom Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sliding Window Median</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Convert the Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minimum Cost to Make Array Equal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Smallest Missing Integer Greater Than Sequential Prefix Sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Single Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Longest Substring with At Least K Repeating Characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minimum Difficulty of a Job Schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Longest Substring of One Repeating Character</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Interleaving String</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Candy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Isomorphic Strings</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Range Sum Query - Immutable</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Maximum Length Substring With Two Occurrences</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Longest Valid Parentheses</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pow(x,n)</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-coins-from-k-consecutive-bags/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-operations-to-make-array-non-decreasing/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-common-prefix/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-product-of-three-numbers/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/palindrome-number/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/add-binary/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/predict-the-winner/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/roman-to-integer/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/reverse-integer/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/running-sum-of-1d-array/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/concatenation-of-array/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/fibonacci-number/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-element/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/stone-game-ii/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-anagram/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/length-of-longest-subarray-with-at-most-k-frequency/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/rotate-image/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/string-to-integer-atoi/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/count-primes/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/smallest-subsequence-of-distinct-characters/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/power-of-two/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/happy-number/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/multiply-strings/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-unique-xor-triplets-ii/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/check-if-array-is-sorted-and-rotated/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/reverse-string/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/smallest-palindromic-rearrangement-i/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/super-washing-machines/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/largest-divisible-subset/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-duplicate-letters/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/kids-with-the-greatest-number-of-candies/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/ones-and-zeroes/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/bulls-and-cows/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-number-of-pushes-to-type-word-ii/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/array-partition/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/widest-possible-fence/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/set-mismatch/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/shortest-subarray-with-sum-at-least-k/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-methods-from-project/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/powx-n/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/ransom-note/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/sliding-window-median/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/convert-the-temperature/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-cost-to-make-array-equal/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/smallest-missing-integer-greater-than-sequential-prefix-sum/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/single-number/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-substring-with-at-least-k-repeating-characters/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-difficulty-of-a-job-schedule/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-substring-of-one-repeating-character/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/interleaving-string/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/candy/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/isomorphic-strings/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/range-sum-query-immutable/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-length-substring-with-two-occurrences/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-valid-parentheses/description/</t>
+  </si>
+  <si>
+    <t>(Set - 2)</t>
   </si>
 </sst>
 </file>
@@ -1475,13 +1820,14 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1858,13 +2204,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="61" customWidth="1"/>
-    <col min="3" max="3" width="59.90625" customWidth="1"/>
-    <col min="4" max="4" width="4.81640625" customWidth="1"/>
+    <col min="3" max="3" width="102.54296875" customWidth="1"/>
+    <col min="4" max="4" width="97.08984375" customWidth="1"/>
     <col min="5" max="5" width="68.26953125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3417,6 +3763,638 @@
       </c>
       <c r="D111" t="s">
         <v>312</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B113" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" t="s">
+        <v>315</v>
+      </c>
+      <c r="C114" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C115" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C116" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C117" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>12</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C118" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>320</v>
+      </c>
+      <c r="C119" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" t="s">
+        <v>321</v>
+      </c>
+      <c r="C120" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" t="s">
+        <v>322</v>
+      </c>
+      <c r="C121" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" t="s">
+        <v>324</v>
+      </c>
+      <c r="C122" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>4</v>
+      </c>
+      <c r="B123" t="s">
+        <v>326</v>
+      </c>
+      <c r="C123" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" t="s">
+        <v>327</v>
+      </c>
+      <c r="C124" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" t="s">
+        <v>318</v>
+      </c>
+      <c r="C125" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" t="s">
+        <v>328</v>
+      </c>
+      <c r="C126" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" t="s">
+        <v>329</v>
+      </c>
+      <c r="C127" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>4</v>
+      </c>
+      <c r="B128" t="s">
+        <v>330</v>
+      </c>
+      <c r="C128" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" t="s">
+        <v>331</v>
+      </c>
+      <c r="C129" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" t="s">
+        <v>333</v>
+      </c>
+      <c r="C130" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" t="s">
+        <v>334</v>
+      </c>
+      <c r="C131" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" t="s">
+        <v>335</v>
+      </c>
+      <c r="C132" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>4</v>
+      </c>
+      <c r="B133" t="s">
+        <v>317</v>
+      </c>
+      <c r="C133" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" t="s">
+        <v>336</v>
+      </c>
+      <c r="C134" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135" t="s">
+        <v>337</v>
+      </c>
+      <c r="C135" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" t="s">
+        <v>338</v>
+      </c>
+      <c r="C136" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" t="s">
+        <v>339</v>
+      </c>
+      <c r="C137" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>4</v>
+      </c>
+      <c r="B138" t="s">
+        <v>340</v>
+      </c>
+      <c r="C138" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" t="s">
+        <v>341</v>
+      </c>
+      <c r="C139" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" t="s">
+        <v>342</v>
+      </c>
+      <c r="C140" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" t="s">
+        <v>343</v>
+      </c>
+      <c r="C141" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" t="s">
+        <v>344</v>
+      </c>
+      <c r="C142" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>4</v>
+      </c>
+      <c r="B143" t="s">
+        <v>345</v>
+      </c>
+      <c r="C143" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>4</v>
+      </c>
+      <c r="B144" t="s">
+        <v>346</v>
+      </c>
+      <c r="C144" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" t="s">
+        <v>347</v>
+      </c>
+      <c r="C145" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" t="s">
+        <v>348</v>
+      </c>
+      <c r="C146" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>12</v>
+      </c>
+      <c r="B147" t="s">
+        <v>349</v>
+      </c>
+      <c r="C147" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>12</v>
+      </c>
+      <c r="B148" t="s">
+        <v>350</v>
+      </c>
+      <c r="C148" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>12</v>
+      </c>
+      <c r="B149" t="s">
+        <v>351</v>
+      </c>
+      <c r="C149" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>4</v>
+      </c>
+      <c r="B150" t="s">
+        <v>352</v>
+      </c>
+      <c r="C150" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" t="s">
+        <v>353</v>
+      </c>
+      <c r="C151" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>4</v>
+      </c>
+      <c r="B152" t="s">
+        <v>354</v>
+      </c>
+      <c r="C152" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" t="s">
+        <v>355</v>
+      </c>
+      <c r="C153" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>12</v>
+      </c>
+      <c r="B154" t="s">
+        <v>356</v>
+      </c>
+      <c r="C154" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>372</v>
+      </c>
+      <c r="C155" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>357</v>
+      </c>
+      <c r="C156" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>4</v>
+      </c>
+      <c r="B157" t="s">
+        <v>358</v>
+      </c>
+      <c r="C157" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" t="s">
+        <v>359</v>
+      </c>
+      <c r="C158" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" t="s">
+        <v>360</v>
+      </c>
+      <c r="C159" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>4</v>
+      </c>
+      <c r="B160" t="s">
+        <v>361</v>
+      </c>
+      <c r="C160" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" t="s">
+        <v>362</v>
+      </c>
+      <c r="C161" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>363</v>
+      </c>
+      <c r="C162" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>364</v>
+      </c>
+      <c r="C163" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>4</v>
+      </c>
+      <c r="B164" t="s">
+        <v>365</v>
+      </c>
+      <c r="C164" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>12</v>
+      </c>
+      <c r="B165" t="s">
+        <v>366</v>
+      </c>
+      <c r="C165" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>4</v>
+      </c>
+      <c r="B166" t="s">
+        <v>367</v>
+      </c>
+      <c r="C166" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>368</v>
+      </c>
+      <c r="C167" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" t="s">
+        <v>369</v>
+      </c>
+      <c r="C168" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>370</v>
+      </c>
+      <c r="C169" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>371</v>
+      </c>
+      <c r="C170" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>

--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE5332E-0A96-4B75-A4A2-409342025B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1808388C-C452-48E6-8491-33AD8817A9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
   <sheets>
     <sheet name="amazon_sde1_filtered_questions" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="426">
   <si>
     <t>Difficulty</t>
   </si>
@@ -1051,9 +1051,6 @@
     <t xml:space="preserve"> Check if Array Is Sorted and Rotated</t>
   </si>
   <si>
-    <t xml:space="preserve"> Reverse String</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Smallest Palindromic Rearrangement I</t>
   </si>
   <si>
@@ -1138,9 +1135,6 @@
     <t xml:space="preserve"> Longest Valid Parentheses</t>
   </si>
   <si>
-    <t xml:space="preserve"> Pow(x,n)</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/maximum-coins-from-k-consecutive-bags/description/</t>
   </si>
   <si>
@@ -1219,9 +1213,6 @@
     <t>https://leetcode.com/problems/check-if-array-is-sorted-and-rotated/description/</t>
   </si>
   <si>
-    <t>https://leetcode.com/problems/reverse-string/description/</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/smallest-palindromic-rearrangement-i/description/</t>
   </si>
   <si>
@@ -1259,9 +1250,6 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/remove-methods-from-project/description/</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/powx-n/description/</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/ransom-note/description/</t>
@@ -1820,14 +1808,13 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2204,17 +2191,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
-  <dimension ref="A1:D170"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D168"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
     <col min="2" max="2" width="61" customWidth="1"/>
-    <col min="3" max="3" width="102.54296875" customWidth="1"/>
-    <col min="4" max="4" width="97.08984375" customWidth="1"/>
-    <col min="5" max="5" width="68.26953125" customWidth="1"/>
+    <col min="3" max="3" width="102.5703125" customWidth="1"/>
+    <col min="4" max="4" width="97.140625" customWidth="1"/>
+    <col min="5" max="5" width="68.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2228,7 +2215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2242,7 +2229,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2256,7 +2243,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2270,7 +2257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2284,7 +2271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2298,7 +2285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2326,7 +2313,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2340,7 +2327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -2354,7 +2341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -2368,7 +2355,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2382,7 +2369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2396,7 +2383,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -2410,7 +2397,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -2424,7 +2411,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -2438,7 +2425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -2452,7 +2439,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -2466,7 +2453,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2480,7 +2467,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2494,7 +2481,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2508,7 +2495,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2522,7 +2509,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2536,7 +2523,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2550,7 +2537,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -2564,7 +2551,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -2578,7 +2565,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -2592,7 +2579,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2606,7 +2593,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -2620,7 +2607,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2634,7 +2621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -2648,7 +2635,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -2662,7 +2649,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -2676,7 +2663,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -2690,7 +2677,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -2704,7 +2691,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -2718,7 +2705,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -2732,7 +2719,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -2746,7 +2733,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -2760,7 +2747,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -2774,7 +2761,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -2788,7 +2775,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -2802,7 +2789,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -2816,7 +2803,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2830,7 +2817,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -2844,7 +2831,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -2858,7 +2845,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -2872,7 +2859,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -2886,7 +2873,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -2900,7 +2887,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -2914,7 +2901,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -2928,7 +2915,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -2942,7 +2929,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2956,7 +2943,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2970,7 +2957,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -2984,7 +2971,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -2998,7 +2985,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -3012,7 +2999,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -3026,7 +3013,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -3040,7 +3027,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -3054,7 +3041,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -3068,7 +3055,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -3082,7 +3069,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -3096,7 +3083,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -3110,7 +3097,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -3124,7 +3111,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -3138,7 +3125,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -3152,7 +3139,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -3166,7 +3153,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -3180,7 +3167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -3194,7 +3181,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -3208,7 +3195,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -3222,7 +3209,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -3236,7 +3223,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -3250,7 +3237,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -3264,7 +3251,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -3278,7 +3265,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -3292,7 +3279,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -3306,7 +3293,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -3320,7 +3307,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -3334,7 +3321,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -3348,7 +3335,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -3362,7 +3349,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3376,7 +3363,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -3390,7 +3377,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3404,7 +3391,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -3418,7 +3405,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -3432,7 +3419,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -3446,7 +3433,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -3460,7 +3447,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -3474,7 +3461,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3488,7 +3475,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -3502,7 +3489,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -3516,7 +3503,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3530,7 +3517,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -3544,7 +3531,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -3558,7 +3545,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -3572,7 +3559,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>12</v>
       </c>
@@ -3583,7 +3570,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -3597,7 +3584,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -3611,7 +3598,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3625,7 +3612,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -3639,7 +3626,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3653,7 +3640,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -3667,7 +3654,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -3681,7 +3668,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3695,7 +3682,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3709,7 +3696,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -3723,7 +3710,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -3737,7 +3724,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>12</v>
       </c>
@@ -3751,7 +3738,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>12</v>
       </c>
@@ -3765,12 +3752,12 @@
         <v>312</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>0</v>
       </c>
@@ -3781,18 +3768,18 @@
         <v>316</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="6" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>8</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>319</v>
       </c>
       <c r="C115" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3800,10 +3787,10 @@
         <v>325</v>
       </c>
       <c r="C116" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -3811,10 +3798,10 @@
         <v>323</v>
       </c>
       <c r="C117" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -3822,579 +3809,557 @@
         <v>332</v>
       </c>
       <c r="C118" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>8</v>
-      </c>
-      <c r="B120" t="s">
-        <v>321</v>
-      </c>
-      <c r="C120" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>8</v>
-      </c>
-      <c r="B121" t="s">
-        <v>322</v>
-      </c>
-      <c r="C121" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>8</v>
-      </c>
-      <c r="B122" t="s">
-        <v>324</v>
-      </c>
-      <c r="C122" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>8</v>
-      </c>
-      <c r="B124" t="s">
-        <v>327</v>
-      </c>
-      <c r="C124" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>8</v>
-      </c>
-      <c r="B125" t="s">
-        <v>318</v>
-      </c>
-      <c r="C125" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>8</v>
-      </c>
-      <c r="B126" t="s">
-        <v>328</v>
-      </c>
-      <c r="C126" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>8</v>
-      </c>
-      <c r="B127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C127" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>4</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C128" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C128" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>8</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>4</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" t="s">
+        <v>343</v>
+      </c>
+      <c r="C138" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>4</v>
+      </c>
+      <c r="B139" t="s">
+        <v>344</v>
+      </c>
+      <c r="C139" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>4</v>
+      </c>
+      <c r="B140" t="s">
+        <v>345</v>
+      </c>
+      <c r="C140" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" t="s">
         <v>331</v>
       </c>
-      <c r="C129" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>8</v>
-      </c>
-      <c r="B130" t="s">
-        <v>333</v>
-      </c>
-      <c r="C130" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>8</v>
-      </c>
-      <c r="B131" t="s">
-        <v>334</v>
-      </c>
-      <c r="C131" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>8</v>
-      </c>
-      <c r="B132" t="s">
-        <v>335</v>
-      </c>
-      <c r="C132" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="C141" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>4</v>
       </c>
-      <c r="B133" t="s">
-        <v>317</v>
-      </c>
-      <c r="C133" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>8</v>
-      </c>
-      <c r="B134" t="s">
-        <v>336</v>
-      </c>
-      <c r="C134" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>8</v>
-      </c>
-      <c r="B135" t="s">
-        <v>337</v>
-      </c>
-      <c r="C135" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>8</v>
-      </c>
-      <c r="B136" t="s">
-        <v>338</v>
-      </c>
-      <c r="C136" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>8</v>
-      </c>
-      <c r="B137" t="s">
-        <v>339</v>
-      </c>
-      <c r="C137" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>4</v>
-      </c>
-      <c r="B138" t="s">
-        <v>340</v>
-      </c>
-      <c r="C138" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>8</v>
-      </c>
-      <c r="B139" t="s">
-        <v>341</v>
-      </c>
-      <c r="C139" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>8</v>
-      </c>
-      <c r="B140" t="s">
-        <v>342</v>
-      </c>
-      <c r="C140" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>8</v>
-      </c>
-      <c r="B141" t="s">
-        <v>343</v>
-      </c>
-      <c r="C141" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>8</v>
-      </c>
       <c r="B142" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C142" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>345</v>
-      </c>
-      <c r="C143" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+        <v>348</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C144" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C145" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>4</v>
       </c>
       <c r="B146" t="s">
-        <v>348</v>
-      </c>
-      <c r="C146" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" t="s">
+        <v>352</v>
+      </c>
+      <c r="C147" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" t="s">
+        <v>353</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>4</v>
+      </c>
+      <c r="B149" t="s">
+        <v>354</v>
+      </c>
+      <c r="C149" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>12</v>
       </c>
-      <c r="B147" t="s">
-        <v>349</v>
-      </c>
-      <c r="C147" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>12</v>
-      </c>
-      <c r="B148" t="s">
-        <v>350</v>
-      </c>
-      <c r="C148" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>12</v>
-      </c>
-      <c r="B149" t="s">
-        <v>351</v>
-      </c>
-      <c r="C149" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>4</v>
-      </c>
       <c r="B150" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C150" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C151" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>4</v>
       </c>
       <c r="B152" t="s">
-        <v>354</v>
-      </c>
-      <c r="C152" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>358</v>
+      </c>
+      <c r="C153" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" t="s">
+        <v>359</v>
+      </c>
+      <c r="C154" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>4</v>
       </c>
-      <c r="B153" t="s">
-        <v>355</v>
-      </c>
-      <c r="C153" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>12</v>
-      </c>
-      <c r="B154" t="s">
-        <v>356</v>
-      </c>
-      <c r="C154" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
       <c r="B155" t="s">
-        <v>372</v>
-      </c>
-      <c r="C155" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>357</v>
-      </c>
-      <c r="C156" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+        <v>341</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>358</v>
-      </c>
-      <c r="C157" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C158" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B159" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C159" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>4</v>
       </c>
       <c r="B160" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C160" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C161" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B162" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C162" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>364</v>
-      </c>
-      <c r="C163" t="s">
+        <v>367</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C164" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C165" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C166" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>368</v>
-      </c>
-      <c r="C167" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B168" t="s">
-        <v>369</v>
-      </c>
-      <c r="C168" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>8</v>
-      </c>
-      <c r="B169" t="s">
-        <v>370</v>
-      </c>
-      <c r="C169" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>8</v>
-      </c>
-      <c r="B170" t="s">
+        <v>317</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="C170" t="s">
-        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -4495,8 +4460,38 @@
     <hyperlink ref="C106" r:id="rId94" xr:uid="{E63386B9-D4BB-4EC2-ABBC-787D5C433C84}"/>
     <hyperlink ref="C111" r:id="rId95" xr:uid="{7B68E9DB-3F88-42AA-A5B8-6C92BC7CCC4A}"/>
     <hyperlink ref="C109" r:id="rId96" xr:uid="{FD6CDB59-0FF2-404F-A390-575C163418DF}"/>
+    <hyperlink ref="C119" r:id="rId97" xr:uid="{E0FC33A2-D03A-48A6-87EF-59600AC38568}"/>
+    <hyperlink ref="C120" r:id="rId98" xr:uid="{0361F1EE-8DEC-4F6E-9D48-121367996FC4}"/>
+    <hyperlink ref="C121" r:id="rId99" xr:uid="{8A9E09A4-D03A-49DB-9C1D-2A335EBCA4F2}"/>
+    <hyperlink ref="C122" r:id="rId100" xr:uid="{AB242CEA-21F9-460F-898A-EA97DE8BE215}"/>
+    <hyperlink ref="C123" r:id="rId101" xr:uid="{FAC6DB05-5341-406B-A923-69D0A6A9F4CF}"/>
+    <hyperlink ref="C124" r:id="rId102" xr:uid="{A12DAF4F-DA53-4C37-A228-B06C66291FCE}"/>
+    <hyperlink ref="C125" r:id="rId103" xr:uid="{3802D333-ED18-449E-9357-390856F2E74F}"/>
+    <hyperlink ref="C126" r:id="rId104" xr:uid="{6DD592D8-7E8E-45B6-A26F-82CB136086DC}"/>
+    <hyperlink ref="C127" r:id="rId105" xr:uid="{687299CA-F5BD-4359-A19B-6739A9EB3A62}"/>
+    <hyperlink ref="C128" r:id="rId106" xr:uid="{9C01EF49-0F81-40FC-ACA2-1B5CEBEAF3C4}"/>
+    <hyperlink ref="C141" r:id="rId107" xr:uid="{A1ED9BDA-ACA5-4B6A-8562-F21A1133879C}"/>
+    <hyperlink ref="C129" r:id="rId108" xr:uid="{B6255BB1-281E-4413-AA60-7F650B88AE31}"/>
+    <hyperlink ref="C130" r:id="rId109" xr:uid="{5C4B4859-6F57-41C9-A767-78BAA0185AC6}"/>
+    <hyperlink ref="C167" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
+    <hyperlink ref="C168" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
+    <hyperlink ref="C131" r:id="rId112" xr:uid="{812567D3-953B-4D03-AE8C-43607B67208C}"/>
+    <hyperlink ref="C132" r:id="rId113" xr:uid="{9F5366E7-2B07-4547-A415-A41154DAF6E8}"/>
+    <hyperlink ref="C133" r:id="rId114" xr:uid="{EC814759-6574-4DB1-9594-36303369F2E3}"/>
+    <hyperlink ref="C134" r:id="rId115" xr:uid="{DEB7B4FE-8BAA-4D7D-A585-E670B6B343C6}"/>
+    <hyperlink ref="C135" r:id="rId116" xr:uid="{7A6C01C3-E500-457E-82AF-768FAC2EE944}"/>
+    <hyperlink ref="C156" r:id="rId117" xr:uid="{AFBF2644-D248-411A-8729-0F8B67DA6166}"/>
+    <hyperlink ref="C157" r:id="rId118" xr:uid="{CF99D9B0-9ED1-49FE-BB38-F2FF4D60ED2D}"/>
+    <hyperlink ref="C136" r:id="rId119" xr:uid="{A48CD043-136D-4259-8BCF-9B9DD1903EBB}"/>
+    <hyperlink ref="C143" r:id="rId120" xr:uid="{81DE305D-88C6-4648-8210-032A2AB897D2}"/>
+    <hyperlink ref="C146" r:id="rId121" xr:uid="{AA4F5772-E99C-4FA5-8C55-0181B3B31431}"/>
+    <hyperlink ref="C148" r:id="rId122" xr:uid="{BB6B1DBE-0790-4C67-B2CD-03C5DF13EE91}"/>
+    <hyperlink ref="C152" r:id="rId123" xr:uid="{D7949A5B-0952-40E7-B0C6-1772D9DCD774}"/>
+    <hyperlink ref="C155" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
+    <hyperlink ref="C137" r:id="rId125" xr:uid="{E17CCA86-EE67-40CC-8E48-F995E9124648}"/>
+    <hyperlink ref="C163" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId97"/>
+  <pageSetup orientation="portrait" r:id="rId127"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1808388C-C452-48E6-8491-33AD8817A9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7D41C4-47D2-4183-A346-FD40DC45B679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -4025,11 +4025,11 @@
       <c r="A138" t="s">
         <v>8</v>
       </c>
-      <c r="B138" t="s">
-        <v>343</v>
-      </c>
-      <c r="C138" t="s">
-        <v>397</v>
+      <c r="B138" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -4292,7 +4292,7 @@
       <c r="B162" t="s">
         <v>366</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="2" t="s">
         <v>420</v>
       </c>
     </row>
@@ -4301,10 +4301,10 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>367</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>421</v>
+        <v>368</v>
+      </c>
+      <c r="C163" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4312,10 +4312,10 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C164" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4323,10 +4323,10 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C165" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4334,32 +4334,32 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>370</v>
-      </c>
-      <c r="C166" t="s">
-        <v>424</v>
+        <v>335</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B167" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>317</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>371</v>
+        <v>343</v>
+      </c>
+      <c r="C168" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -4473,8 +4473,8 @@
     <hyperlink ref="C141" r:id="rId107" xr:uid="{A1ED9BDA-ACA5-4B6A-8562-F21A1133879C}"/>
     <hyperlink ref="C129" r:id="rId108" xr:uid="{B6255BB1-281E-4413-AA60-7F650B88AE31}"/>
     <hyperlink ref="C130" r:id="rId109" xr:uid="{5C4B4859-6F57-41C9-A767-78BAA0185AC6}"/>
-    <hyperlink ref="C167" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
-    <hyperlink ref="C168" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
+    <hyperlink ref="C166" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
+    <hyperlink ref="C167" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
     <hyperlink ref="C131" r:id="rId112" xr:uid="{812567D3-953B-4D03-AE8C-43607B67208C}"/>
     <hyperlink ref="C132" r:id="rId113" xr:uid="{9F5366E7-2B07-4547-A415-A41154DAF6E8}"/>
     <hyperlink ref="C133" r:id="rId114" xr:uid="{EC814759-6574-4DB1-9594-36303369F2E3}"/>
@@ -4489,9 +4489,10 @@
     <hyperlink ref="C152" r:id="rId123" xr:uid="{D7949A5B-0952-40E7-B0C6-1772D9DCD774}"/>
     <hyperlink ref="C155" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
     <hyperlink ref="C137" r:id="rId125" xr:uid="{E17CCA86-EE67-40CC-8E48-F995E9124648}"/>
-    <hyperlink ref="C163" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
+    <hyperlink ref="C138" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
+    <hyperlink ref="C162" r:id="rId127" xr:uid="{135DD339-026F-4D89-8A58-A0DAC0070079}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId127"/>
+  <pageSetup orientation="portrait" r:id="rId128"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7D41C4-47D2-4183-A346-FD40DC45B679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C38715-FABA-4173-8898-B27B5B8F785B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
   <sheets>
     <sheet name="amazon_sde1_filtered_questions" sheetId="1" r:id="rId1"/>
@@ -2192,16 +2192,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
   <dimension ref="A1:D168"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="61" customWidth="1"/>
-    <col min="3" max="3" width="102.5703125" customWidth="1"/>
-    <col min="4" max="4" width="97.140625" customWidth="1"/>
-    <col min="5" max="5" width="68.28515625" customWidth="1"/>
+    <col min="3" max="3" width="102.54296875" customWidth="1"/>
+    <col min="4" max="4" width="97.1796875" customWidth="1"/>
+    <col min="5" max="5" width="68.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>12</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>12</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>12</v>
       </c>
@@ -3752,12 +3752,12 @@
         <v>312</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>0</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>8</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>8</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>8</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>8</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>8</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>8</v>
       </c>
@@ -4032,95 +4032,95 @@
         <v>421</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>4</v>
       </c>
-      <c r="B139" t="s">
-        <v>344</v>
-      </c>
-      <c r="C139" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B139" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>4</v>
       </c>
-      <c r="B140" t="s">
-        <v>345</v>
-      </c>
-      <c r="C140" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B140" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>8</v>
-      </c>
-      <c r="B141" t="s">
-        <v>331</v>
+        <v>4</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>4</v>
-      </c>
-      <c r="B142" t="s">
-        <v>347</v>
-      </c>
-      <c r="C142" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>12</v>
       </c>
-      <c r="B143" t="s">
-        <v>348</v>
+      <c r="B143" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>4</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>12</v>
       </c>
-      <c r="B144" t="s">
-        <v>349</v>
-      </c>
-      <c r="C144" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>12</v>
-      </c>
-      <c r="B145" t="s">
+      <c r="B146" t="s">
         <v>350</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C146" s="2" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>4</v>
-      </c>
-      <c r="B146" t="s">
-        <v>351</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -4142,18 +4142,18 @@
         <v>407</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>4</v>
       </c>
       <c r="B149" t="s">
         <v>354</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="2" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>12</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>8</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>8</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>8</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>8</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>8</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>4</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>12</v>
       </c>
@@ -4285,18 +4285,18 @@
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>8</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>8</v>
       </c>
@@ -4318,48 +4318,48 @@
         <v>423</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>370</v>
-      </c>
-      <c r="C165" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B166" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>343</v>
+      </c>
+      <c r="C167" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
         <v>4</v>
       </c>
-      <c r="B167" t="s">
-        <v>317</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>8</v>
-      </c>
       <c r="B168" t="s">
-        <v>343</v>
-      </c>
-      <c r="C168" t="s">
-        <v>397</v>
+        <v>344</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -4470,11 +4470,11 @@
     <hyperlink ref="C126" r:id="rId104" xr:uid="{6DD592D8-7E8E-45B6-A26F-82CB136086DC}"/>
     <hyperlink ref="C127" r:id="rId105" xr:uid="{687299CA-F5BD-4359-A19B-6739A9EB3A62}"/>
     <hyperlink ref="C128" r:id="rId106" xr:uid="{9C01EF49-0F81-40FC-ACA2-1B5CEBEAF3C4}"/>
-    <hyperlink ref="C141" r:id="rId107" xr:uid="{A1ED9BDA-ACA5-4B6A-8562-F21A1133879C}"/>
+    <hyperlink ref="C162" r:id="rId107" xr:uid="{A1ED9BDA-ACA5-4B6A-8562-F21A1133879C}"/>
     <hyperlink ref="C129" r:id="rId108" xr:uid="{B6255BB1-281E-4413-AA60-7F650B88AE31}"/>
     <hyperlink ref="C130" r:id="rId109" xr:uid="{5C4B4859-6F57-41C9-A767-78BAA0185AC6}"/>
-    <hyperlink ref="C166" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
-    <hyperlink ref="C167" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
+    <hyperlink ref="C165" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
+    <hyperlink ref="C166" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
     <hyperlink ref="C131" r:id="rId112" xr:uid="{812567D3-953B-4D03-AE8C-43607B67208C}"/>
     <hyperlink ref="C132" r:id="rId113" xr:uid="{9F5366E7-2B07-4547-A415-A41154DAF6E8}"/>
     <hyperlink ref="C133" r:id="rId114" xr:uid="{EC814759-6574-4DB1-9594-36303369F2E3}"/>
@@ -4483,16 +4483,23 @@
     <hyperlink ref="C156" r:id="rId117" xr:uid="{AFBF2644-D248-411A-8729-0F8B67DA6166}"/>
     <hyperlink ref="C157" r:id="rId118" xr:uid="{CF99D9B0-9ED1-49FE-BB38-F2FF4D60ED2D}"/>
     <hyperlink ref="C136" r:id="rId119" xr:uid="{A48CD043-136D-4259-8BCF-9B9DD1903EBB}"/>
-    <hyperlink ref="C143" r:id="rId120" xr:uid="{81DE305D-88C6-4648-8210-032A2AB897D2}"/>
-    <hyperlink ref="C146" r:id="rId121" xr:uid="{AA4F5772-E99C-4FA5-8C55-0181B3B31431}"/>
+    <hyperlink ref="C142" r:id="rId120" xr:uid="{81DE305D-88C6-4648-8210-032A2AB897D2}"/>
+    <hyperlink ref="C145" r:id="rId121" xr:uid="{AA4F5772-E99C-4FA5-8C55-0181B3B31431}"/>
     <hyperlink ref="C148" r:id="rId122" xr:uid="{BB6B1DBE-0790-4C67-B2CD-03C5DF13EE91}"/>
     <hyperlink ref="C152" r:id="rId123" xr:uid="{D7949A5B-0952-40E7-B0C6-1772D9DCD774}"/>
     <hyperlink ref="C155" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
     <hyperlink ref="C137" r:id="rId125" xr:uid="{E17CCA86-EE67-40CC-8E48-F995E9124648}"/>
     <hyperlink ref="C138" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
-    <hyperlink ref="C162" r:id="rId127" xr:uid="{135DD339-026F-4D89-8A58-A0DAC0070079}"/>
+    <hyperlink ref="C141" r:id="rId127" xr:uid="{135DD339-026F-4D89-8A58-A0DAC0070079}"/>
+    <hyperlink ref="C144" r:id="rId128" xr:uid="{CA906D41-EBEE-4DBF-AF9C-825A4EACE5D9}"/>
+    <hyperlink ref="C168" r:id="rId129" xr:uid="{2A4866D6-0938-4980-B2F8-C2D12CDF93FE}"/>
+    <hyperlink ref="C139" r:id="rId130" xr:uid="{944E35D1-9505-439F-B4D5-13DC55ECD476}"/>
+    <hyperlink ref="C140" r:id="rId131" xr:uid="{5CA067C0-559D-49DD-9CBC-05FF25FDB146}"/>
+    <hyperlink ref="C143" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
+    <hyperlink ref="C146" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
+    <hyperlink ref="C149" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId128"/>
+  <pageSetup orientation="portrait" r:id="rId135"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C38715-FABA-4173-8898-B27B5B8F785B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C378C974-12D8-4D46-BF06-309B8E32224D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -4113,7 +4113,7 @@
       <c r="A146" t="s">
         <v>12</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="1" t="s">
         <v>350</v>
       </c>
       <c r="C146" s="2" t="s">
@@ -4127,7 +4127,7 @@
       <c r="B147" t="s">
         <v>352</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="2" t="s">
         <v>406</v>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       <c r="A148" t="s">
         <v>4</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="1" t="s">
         <v>353</v>
       </c>
       <c r="C148" s="2" t="s">
@@ -4146,7 +4146,7 @@
       <c r="A149" t="s">
         <v>4</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="1" t="s">
         <v>354</v>
       </c>
       <c r="C149" s="2" t="s">
@@ -4498,8 +4498,9 @@
     <hyperlink ref="C143" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
     <hyperlink ref="C146" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
     <hyperlink ref="C149" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
+    <hyperlink ref="C147" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId135"/>
+  <pageSetup orientation="portrait" r:id="rId136"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C378C974-12D8-4D46-BF06-309B8E32224D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9589E6-FA6C-4C27-9D05-C174FDC0D5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -2196,7 +2196,7 @@
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="61" customWidth="1"/>
-    <col min="3" max="3" width="102.54296875" customWidth="1"/>
+    <col min="3" max="3" width="85" customWidth="1"/>
     <col min="4" max="4" width="97.1796875" customWidth="1"/>
     <col min="5" max="5" width="68.26953125" customWidth="1"/>
   </cols>
@@ -3758,13 +3758,13 @@
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="3" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4122,13 +4122,13 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>8</v>
-      </c>
-      <c r="B147" t="s">
-        <v>352</v>
+        <v>4</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -4136,21 +4136,21 @@
         <v>4</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -4160,7 +4160,7 @@
       <c r="B150" t="s">
         <v>355</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="2" t="s">
         <v>409</v>
       </c>
     </row>
@@ -4169,10 +4169,10 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>356</v>
-      </c>
-      <c r="C151" t="s">
-        <v>410</v>
+        <v>352</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4485,7 +4485,7 @@
     <hyperlink ref="C136" r:id="rId119" xr:uid="{A48CD043-136D-4259-8BCF-9B9DD1903EBB}"/>
     <hyperlink ref="C142" r:id="rId120" xr:uid="{81DE305D-88C6-4648-8210-032A2AB897D2}"/>
     <hyperlink ref="C145" r:id="rId121" xr:uid="{AA4F5772-E99C-4FA5-8C55-0181B3B31431}"/>
-    <hyperlink ref="C148" r:id="rId122" xr:uid="{BB6B1DBE-0790-4C67-B2CD-03C5DF13EE91}"/>
+    <hyperlink ref="C147" r:id="rId122" xr:uid="{BB6B1DBE-0790-4C67-B2CD-03C5DF13EE91}"/>
     <hyperlink ref="C152" r:id="rId123" xr:uid="{D7949A5B-0952-40E7-B0C6-1772D9DCD774}"/>
     <hyperlink ref="C155" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
     <hyperlink ref="C137" r:id="rId125" xr:uid="{E17CCA86-EE67-40CC-8E48-F995E9124648}"/>
@@ -4497,10 +4497,12 @@
     <hyperlink ref="C140" r:id="rId131" xr:uid="{5CA067C0-559D-49DD-9CBC-05FF25FDB146}"/>
     <hyperlink ref="C143" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
     <hyperlink ref="C146" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
-    <hyperlink ref="C149" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
-    <hyperlink ref="C147" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
+    <hyperlink ref="C148" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
+    <hyperlink ref="C151" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
+    <hyperlink ref="C150" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
+    <hyperlink ref="C149" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId136"/>
+  <pageSetup orientation="portrait" r:id="rId138"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9589E6-FA6C-4C27-9D05-C174FDC0D5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33523F8-2521-4655-97DC-46080B356F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="428">
   <si>
     <t>Difficulty</t>
   </si>
@@ -1298,6 +1298,12 @@
   </si>
   <si>
     <t>(Set - 2)</t>
+  </si>
+  <si>
+    <t>Most Profitable Path in a Tree</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/most-profitable-path-in-a-tree/description/</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
@@ -4155,24 +4161,24 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>12</v>
-      </c>
-      <c r="B150" t="s">
-        <v>355</v>
+        <v>8</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>8</v>
       </c>
-      <c r="B151" t="s">
-        <v>352</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>406</v>
+      <c r="B151" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C151" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4191,10 +4197,10 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>358</v>
-      </c>
-      <c r="C153" t="s">
-        <v>412</v>
+        <v>352</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4360,6 +4366,17 @@
       </c>
       <c r="C168" s="2" t="s">
         <v>398</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>12</v>
+      </c>
+      <c r="B169" t="s">
+        <v>355</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -4498,11 +4515,12 @@
     <hyperlink ref="C143" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
     <hyperlink ref="C146" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
     <hyperlink ref="C148" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
-    <hyperlink ref="C151" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
-    <hyperlink ref="C150" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
+    <hyperlink ref="C153" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
+    <hyperlink ref="C169" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
     <hyperlink ref="C149" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
+    <hyperlink ref="C150" r:id="rId138" xr:uid="{FA524709-47E9-490F-A089-312860B0DC84}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId138"/>
+  <pageSetup orientation="portrait" r:id="rId139"/>
 </worksheet>
 </file>